--- a/data/raw/sales/Week 18/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 18/Audio_Array/other_channels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Week 18 (2)\Week 18\raw\sales\Week 18\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 18\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE7182F-1D4C-484A-BBAD-4AD88C5DAF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562134BA-0489-47E8-BD6A-12FA25853872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="359">
   <si>
     <t>SKU</t>
   </si>
@@ -274,9 +274,6 @@
   </si>
   <si>
     <t>AM-W24</t>
-  </si>
-  <si>
-    <t>AI-04</t>
   </si>
   <si>
     <t>Carlton</t>
@@ -1129,7 +1126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1180,12 +1177,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -1285,7 +1276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1333,17 +1324,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1352,7 +1334,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1993,7 +1975,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:X916"/>
+  <dimension ref="A1:X909"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -2044,146 +2026,165 @@
       <c r="X1" s="4"/>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="19">
-        <v>2</v>
-      </c>
-      <c r="F2" s="20">
-        <v>8642.3700000000008</v>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="19">
-        <v>21</v>
-      </c>
-      <c r="F3" s="20">
-        <v>33795.760000000002</v>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>11436</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="19">
-        <v>5</v>
-      </c>
-      <c r="F4" s="20">
-        <v>11266.95</v>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>9149</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="18" t="s">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="19">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="20">
-        <v>4066.95</v>
+      <c r="F5">
+        <v>4067</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>17888</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7">
         <v>4</v>
       </c>
-      <c r="F6" s="20">
-        <v>11925.42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="19">
-        <v>3</v>
-      </c>
-      <c r="F7" s="20">
-        <v>4022.88</v>
+      <c r="F7">
+        <v>6437</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3084,13 +3085,6 @@
     <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3165,12 +3159,12 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="26">
         <v>473293.13</v>
       </c>
       <c r="G2">
@@ -3188,12 +3182,12 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="26">
         <v>345585.4</v>
       </c>
       <c r="G3">
@@ -3202,21 +3196,21 @@
     </row>
     <row r="4" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" t="s">
         <v>240</v>
       </c>
-      <c r="B4" t="s">
-        <v>241</v>
-      </c>
       <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
         <v>96</v>
       </c>
-      <c r="D4" t="s">
-        <v>97</v>
-      </c>
       <c r="E4" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="26">
         <v>201666.24</v>
       </c>
       <c r="G4">
@@ -3234,12 +3228,12 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="26">
         <v>198283.13</v>
       </c>
       <c r="G5">
@@ -3257,12 +3251,12 @@
         <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="26">
         <v>151241.56</v>
       </c>
       <c r="G6">
@@ -3280,12 +3274,12 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="26">
         <v>121972.78</v>
       </c>
       <c r="G7">
@@ -3294,21 +3288,21 @@
     </row>
     <row r="8" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B8" t="s">
         <v>242</v>
       </c>
-      <c r="B8" t="s">
-        <v>243</v>
-      </c>
       <c r="C8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" t="s">
         <v>101</v>
       </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
       <c r="E8" t="s">
         <v>71</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="26">
         <v>63542.400000000001</v>
       </c>
       <c r="G8">
@@ -3326,12 +3320,12 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="26">
         <v>59644</v>
       </c>
       <c r="G9">
@@ -3349,12 +3343,12 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="26">
         <v>48782.879999999997</v>
       </c>
       <c r="G10">
@@ -3363,21 +3357,21 @@
     </row>
     <row r="11" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" t="s">
         <v>244</v>
       </c>
-      <c r="B11" t="s">
-        <v>245</v>
-      </c>
       <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
         <v>105</v>
       </c>
-      <c r="D11" t="s">
-        <v>106</v>
-      </c>
       <c r="E11" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="26">
         <v>38211.81</v>
       </c>
       <c r="G11">
@@ -3386,21 +3380,21 @@
     </row>
     <row r="12" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B12" t="s">
         <v>246</v>
       </c>
-      <c r="B12" t="s">
-        <v>247</v>
-      </c>
       <c r="C12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" t="s">
         <v>107</v>
       </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
       <c r="E12" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="26">
         <v>37366.980000000003</v>
       </c>
       <c r="G12">
@@ -3418,12 +3412,12 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="26">
         <v>35414.400000000001</v>
       </c>
       <c r="G13">
@@ -3432,21 +3426,21 @@
     </row>
     <row r="14" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>247</v>
+      </c>
+      <c r="B14" t="s">
         <v>248</v>
       </c>
-      <c r="B14" t="s">
-        <v>249</v>
-      </c>
       <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
         <v>110</v>
       </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
       <c r="E14" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="26">
         <v>34042.370000000003</v>
       </c>
       <c r="G14">
@@ -3455,21 +3449,21 @@
     </row>
     <row r="15" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B15" t="s">
         <v>250</v>
       </c>
-      <c r="B15" t="s">
-        <v>251</v>
-      </c>
       <c r="C15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" t="s">
         <v>112</v>
       </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
       <c r="E15" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="26">
         <v>33894.92</v>
       </c>
       <c r="G15">
@@ -3478,21 +3472,21 @@
     </row>
     <row r="16" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" t="s">
         <v>252</v>
       </c>
-      <c r="B16" t="s">
-        <v>253</v>
-      </c>
       <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" t="s">
         <v>114</v>
       </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
       <c r="E16" t="s">
         <v>71</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="26">
         <v>27957.599999999999</v>
       </c>
       <c r="G16">
@@ -3501,21 +3495,21 @@
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>253</v>
+      </c>
+      <c r="B17" t="s">
         <v>254</v>
       </c>
-      <c r="B17" t="s">
-        <v>255</v>
-      </c>
       <c r="C17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" t="s">
         <v>116</v>
       </c>
-      <c r="D17" t="s">
-        <v>117</v>
-      </c>
       <c r="E17" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="26">
         <v>25746.52</v>
       </c>
       <c r="G17">
@@ -3524,21 +3518,21 @@
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" t="s">
         <v>256</v>
       </c>
-      <c r="B18" t="s">
-        <v>257</v>
-      </c>
       <c r="C18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" t="s">
         <v>118</v>
       </c>
-      <c r="D18" t="s">
-        <v>119</v>
-      </c>
       <c r="E18" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="26">
         <v>25328.01</v>
       </c>
       <c r="G18">
@@ -3547,21 +3541,21 @@
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B19" t="s">
         <v>258</v>
       </c>
-      <c r="B19" t="s">
-        <v>259</v>
-      </c>
       <c r="C19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" t="s">
         <v>120</v>
       </c>
-      <c r="D19" t="s">
-        <v>121</v>
-      </c>
       <c r="E19" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="26">
         <v>23262.66</v>
       </c>
       <c r="G19">
@@ -3579,12 +3573,12 @@
         <v>37</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
         <v>71</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="26">
         <v>22354.2</v>
       </c>
       <c r="G20">
@@ -3593,21 +3587,21 @@
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B21" t="s">
         <v>260</v>
       </c>
-      <c r="B21" t="s">
-        <v>261</v>
-      </c>
       <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" t="s">
         <v>123</v>
       </c>
-      <c r="D21" t="s">
-        <v>124</v>
-      </c>
       <c r="E21" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="26">
         <v>21178</v>
       </c>
       <c r="G21">
@@ -3616,21 +3610,21 @@
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" t="s">
         <v>262</v>
       </c>
-      <c r="B22" t="s">
-        <v>263</v>
-      </c>
       <c r="C22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" t="s">
         <v>125</v>
       </c>
-      <c r="D22" t="s">
-        <v>126</v>
-      </c>
       <c r="E22" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="26">
         <v>19490.68</v>
       </c>
       <c r="G22">
@@ -3639,21 +3633,21 @@
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>263</v>
+      </c>
+      <c r="B23" t="s">
         <v>264</v>
       </c>
-      <c r="B23" t="s">
-        <v>265</v>
-      </c>
       <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
         <v>127</v>
       </c>
-      <c r="D23" t="s">
-        <v>128</v>
-      </c>
       <c r="E23" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="26">
         <v>18969.47</v>
       </c>
       <c r="G23">
@@ -3662,21 +3656,21 @@
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>265</v>
+      </c>
+      <c r="B24" t="s">
         <v>266</v>
       </c>
-      <c r="B24" t="s">
-        <v>267</v>
-      </c>
       <c r="C24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" t="s">
         <v>129</v>
       </c>
-      <c r="D24" t="s">
-        <v>130</v>
-      </c>
       <c r="E24" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="26">
         <v>17178.849999999999</v>
       </c>
       <c r="G24">
@@ -3685,21 +3679,21 @@
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>267</v>
+      </c>
+      <c r="B25" t="s">
         <v>268</v>
       </c>
-      <c r="B25" t="s">
-        <v>269</v>
-      </c>
       <c r="C25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" t="s">
         <v>131</v>
       </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
       <c r="E25" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="26">
         <v>16940.689999999999</v>
       </c>
       <c r="G25">
@@ -3708,21 +3702,21 @@
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B26" t="s">
         <v>270</v>
       </c>
-      <c r="B26" t="s">
-        <v>271</v>
-      </c>
       <c r="C26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" t="s">
         <v>133</v>
       </c>
-      <c r="D26" t="s">
-        <v>134</v>
-      </c>
       <c r="E26" t="s">
         <v>71</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="26">
         <v>15251.7</v>
       </c>
       <c r="G26">
@@ -3740,12 +3734,12 @@
         <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
         <v>71</v>
       </c>
-      <c r="F27" s="29">
+      <c r="F27" s="26">
         <v>14614.4</v>
       </c>
       <c r="G27">
@@ -3754,21 +3748,21 @@
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>271</v>
+      </c>
+      <c r="B28" t="s">
         <v>272</v>
       </c>
-      <c r="B28" t="s">
-        <v>273</v>
-      </c>
       <c r="C28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" t="s">
         <v>136</v>
       </c>
-      <c r="D28" t="s">
-        <v>137</v>
-      </c>
       <c r="E28" t="s">
         <v>71</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="26">
         <v>14486.46</v>
       </c>
       <c r="G28">
@@ -3786,12 +3780,12 @@
         <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
         <v>71</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="26">
         <v>13099.16</v>
       </c>
       <c r="G29">
@@ -3800,21 +3794,21 @@
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>273</v>
+      </c>
+      <c r="B30" t="s">
         <v>274</v>
       </c>
-      <c r="B30" t="s">
-        <v>275</v>
-      </c>
       <c r="C30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" t="s">
         <v>139</v>
       </c>
-      <c r="D30" t="s">
-        <v>140</v>
-      </c>
       <c r="E30" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="26">
         <v>12709.32</v>
       </c>
       <c r="G30">
@@ -3823,21 +3817,21 @@
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>275</v>
+      </c>
+      <c r="B31" t="s">
         <v>276</v>
       </c>
-      <c r="B31" t="s">
-        <v>277</v>
-      </c>
       <c r="C31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" t="s">
         <v>141</v>
       </c>
-      <c r="D31" t="s">
-        <v>142</v>
-      </c>
       <c r="E31" t="s">
         <v>71</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="26">
         <v>12460.05</v>
       </c>
       <c r="G31">
@@ -3846,21 +3840,21 @@
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>277</v>
+      </c>
+      <c r="B32" t="s">
         <v>278</v>
       </c>
-      <c r="B32" t="s">
-        <v>279</v>
-      </c>
       <c r="C32" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" t="s">
         <v>143</v>
       </c>
-      <c r="D32" t="s">
-        <v>144</v>
-      </c>
       <c r="E32" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="26">
         <v>11631.35</v>
       </c>
       <c r="G32">
@@ -3869,21 +3863,21 @@
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>279</v>
+      </c>
+      <c r="B33" t="s">
         <v>280</v>
       </c>
-      <c r="B33" t="s">
-        <v>281</v>
-      </c>
       <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
         <v>145</v>
       </c>
-      <c r="D33" t="s">
-        <v>146</v>
-      </c>
       <c r="E33" t="s">
         <v>71</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="26">
         <v>11522.04</v>
       </c>
       <c r="G33">
@@ -3892,21 +3886,21 @@
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>281</v>
+      </c>
+      <c r="B34" t="s">
         <v>282</v>
       </c>
-      <c r="B34" t="s">
-        <v>283</v>
-      </c>
       <c r="C34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" t="s">
         <v>147</v>
       </c>
-      <c r="D34" t="s">
-        <v>148</v>
-      </c>
       <c r="E34" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="26">
         <v>11518.68</v>
       </c>
       <c r="G34">
@@ -3915,21 +3909,21 @@
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" t="s">
         <v>81</v>
       </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>82</v>
-      </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
         <v>71</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="26">
         <v>10166.94</v>
       </c>
       <c r="G35">
@@ -3938,21 +3932,21 @@
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>283</v>
+      </c>
+      <c r="B36" t="s">
         <v>284</v>
       </c>
-      <c r="B36" t="s">
-        <v>285</v>
-      </c>
       <c r="C36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" t="s">
         <v>150</v>
       </c>
-      <c r="D36" t="s">
-        <v>151</v>
-      </c>
       <c r="E36" t="s">
         <v>71</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="26">
         <v>10166.1</v>
       </c>
       <c r="G36">
@@ -3970,12 +3964,12 @@
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E37" t="s">
         <v>71</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="26">
         <v>9912.7199999999993</v>
       </c>
       <c r="G37">
@@ -3984,21 +3978,21 @@
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" t="s">
         <v>286</v>
       </c>
-      <c r="B38" t="s">
-        <v>287</v>
-      </c>
       <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" t="s">
         <v>153</v>
       </c>
-      <c r="D38" t="s">
-        <v>154</v>
-      </c>
       <c r="E38" t="s">
         <v>71</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="26">
         <v>9829.66</v>
       </c>
       <c r="G38">
@@ -4007,21 +4001,21 @@
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>287</v>
+      </c>
+      <c r="B39" t="s">
         <v>288</v>
       </c>
-      <c r="B39" t="s">
-        <v>289</v>
-      </c>
       <c r="C39" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" t="s">
         <v>155</v>
       </c>
-      <c r="D39" t="s">
-        <v>156</v>
-      </c>
       <c r="E39" t="s">
         <v>71</v>
       </c>
-      <c r="F39" s="29">
+      <c r="F39" s="26">
         <v>9404.23</v>
       </c>
       <c r="G39">
@@ -4030,21 +4024,21 @@
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>289</v>
+      </c>
+      <c r="B40" t="s">
         <v>290</v>
       </c>
-      <c r="B40" t="s">
-        <v>291</v>
-      </c>
       <c r="C40" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" t="s">
         <v>157</v>
       </c>
-      <c r="D40" t="s">
-        <v>158</v>
-      </c>
       <c r="E40" t="s">
         <v>71</v>
       </c>
-      <c r="F40" s="29">
+      <c r="F40" s="26">
         <v>9320.33</v>
       </c>
       <c r="G40">
@@ -4062,12 +4056,12 @@
         <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E41" t="s">
         <v>71</v>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="26">
         <v>9186.44</v>
       </c>
       <c r="G41">
@@ -4076,21 +4070,21 @@
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>291</v>
+      </c>
+      <c r="B42" t="s">
         <v>292</v>
       </c>
-      <c r="B42" t="s">
-        <v>293</v>
-      </c>
       <c r="C42" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" t="s">
         <v>160</v>
       </c>
-      <c r="D42" t="s">
-        <v>161</v>
-      </c>
       <c r="E42" t="s">
         <v>71</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="26">
         <v>9150.84</v>
       </c>
       <c r="G42">
@@ -4099,21 +4093,21 @@
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" t="s">
         <v>294</v>
       </c>
-      <c r="B43" t="s">
-        <v>295</v>
-      </c>
       <c r="C43" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" t="s">
         <v>162</v>
       </c>
-      <c r="D43" t="s">
-        <v>163</v>
-      </c>
       <c r="E43" t="s">
         <v>71</v>
       </c>
-      <c r="F43" s="29">
+      <c r="F43" s="26">
         <v>9150</v>
       </c>
       <c r="G43">
@@ -4122,21 +4116,21 @@
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>295</v>
+      </c>
+      <c r="B44" t="s">
         <v>296</v>
       </c>
-      <c r="B44" t="s">
-        <v>297</v>
-      </c>
       <c r="C44" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" t="s">
         <v>164</v>
       </c>
-      <c r="D44" t="s">
-        <v>165</v>
-      </c>
       <c r="E44" t="s">
         <v>71</v>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="26">
         <v>8050</v>
       </c>
       <c r="G44">
@@ -4154,12 +4148,12 @@
         <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
         <v>71</v>
       </c>
-      <c r="F45" s="29">
+      <c r="F45" s="26">
         <v>8042.4</v>
       </c>
       <c r="G45">
@@ -4168,21 +4162,21 @@
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>297</v>
+      </c>
+      <c r="B46" t="s">
         <v>298</v>
       </c>
-      <c r="B46" t="s">
-        <v>299</v>
-      </c>
       <c r="C46" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" t="s">
         <v>167</v>
       </c>
-      <c r="D46" t="s">
-        <v>168</v>
-      </c>
       <c r="E46" t="s">
         <v>71</v>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="26">
         <v>7243.22</v>
       </c>
       <c r="G46">
@@ -4200,12 +4194,12 @@
         <v>64</v>
       </c>
       <c r="D47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E47" t="s">
         <v>71</v>
       </c>
-      <c r="F47" s="29">
+      <c r="F47" s="26">
         <v>7112.7</v>
       </c>
       <c r="G47">
@@ -4214,21 +4208,21 @@
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>299</v>
+      </c>
+      <c r="B48" t="s">
         <v>300</v>
       </c>
-      <c r="B48" t="s">
-        <v>301</v>
-      </c>
       <c r="C48" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" t="s">
         <v>170</v>
       </c>
-      <c r="D48" t="s">
-        <v>171</v>
-      </c>
       <c r="E48" t="s">
         <v>71</v>
       </c>
-      <c r="F48" s="29">
+      <c r="F48" s="26">
         <v>6777.96</v>
       </c>
       <c r="G48">
@@ -4237,21 +4231,21 @@
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>301</v>
+      </c>
+      <c r="B49" t="s">
         <v>302</v>
       </c>
-      <c r="B49" t="s">
-        <v>303</v>
-      </c>
       <c r="C49" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" t="s">
         <v>172</v>
       </c>
-      <c r="D49" t="s">
-        <v>173</v>
-      </c>
       <c r="E49" t="s">
         <v>71</v>
       </c>
-      <c r="F49" s="29">
+      <c r="F49" s="26">
         <v>6777.96</v>
       </c>
       <c r="G49">
@@ -4260,21 +4254,21 @@
     </row>
     <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>303</v>
+      </c>
+      <c r="B50" t="s">
         <v>304</v>
       </c>
-      <c r="B50" t="s">
-        <v>305</v>
-      </c>
       <c r="C50" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" t="s">
         <v>174</v>
       </c>
-      <c r="D50" t="s">
-        <v>175</v>
-      </c>
       <c r="E50" t="s">
         <v>71</v>
       </c>
-      <c r="F50" s="29">
+      <c r="F50" s="26">
         <v>6777.96</v>
       </c>
       <c r="G50">
@@ -4283,21 +4277,21 @@
     </row>
     <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>305</v>
+      </c>
+      <c r="B51" t="s">
         <v>306</v>
       </c>
-      <c r="B51" t="s">
-        <v>307</v>
-      </c>
       <c r="C51" t="s">
+        <v>175</v>
+      </c>
+      <c r="D51" t="s">
         <v>176</v>
       </c>
-      <c r="D51" t="s">
-        <v>177</v>
-      </c>
       <c r="E51" t="s">
         <v>71</v>
       </c>
-      <c r="F51" s="29">
+      <c r="F51" s="26">
         <v>6776.27</v>
       </c>
       <c r="G51">
@@ -4315,12 +4309,12 @@
         <v>52</v>
       </c>
       <c r="D52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E52" t="s">
         <v>71</v>
       </c>
-      <c r="F52" s="29">
+      <c r="F52" s="26">
         <v>6605.08</v>
       </c>
       <c r="G52">
@@ -4329,21 +4323,21 @@
     </row>
     <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" t="s">
         <v>87</v>
       </c>
-      <c r="B53" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" t="s">
-        <v>88</v>
-      </c>
       <c r="D53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E53" t="s">
         <v>71</v>
       </c>
-      <c r="F53" s="29">
+      <c r="F53" s="26">
         <v>6438.99</v>
       </c>
       <c r="G53">
@@ -4352,21 +4346,21 @@
     </row>
     <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>307</v>
+      </c>
+      <c r="B54" t="s">
         <v>308</v>
       </c>
-      <c r="B54" t="s">
-        <v>309</v>
-      </c>
       <c r="C54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" t="s">
         <v>180</v>
       </c>
-      <c r="D54" t="s">
-        <v>181</v>
-      </c>
       <c r="E54" t="s">
         <v>71</v>
       </c>
-      <c r="F54" s="29">
+      <c r="F54" s="26">
         <v>6353.4</v>
       </c>
       <c r="G54">
@@ -4384,12 +4378,12 @@
         <v>67</v>
       </c>
       <c r="D55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E55" t="s">
         <v>71</v>
       </c>
-      <c r="F55" s="29">
+      <c r="F55" s="26">
         <v>6015.25</v>
       </c>
       <c r="G55">
@@ -4398,21 +4392,21 @@
     </row>
     <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>309</v>
+      </c>
+      <c r="B56" t="s">
         <v>310</v>
       </c>
-      <c r="B56" t="s">
-        <v>311</v>
-      </c>
       <c r="C56" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="s">
         <v>183</v>
       </c>
-      <c r="D56" t="s">
-        <v>184</v>
-      </c>
       <c r="E56" t="s">
         <v>71</v>
       </c>
-      <c r="F56" s="29">
+      <c r="F56" s="26">
         <v>5931.36</v>
       </c>
       <c r="G56">
@@ -4421,21 +4415,21 @@
     </row>
     <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>311</v>
+      </c>
+      <c r="B57" t="s">
         <v>312</v>
       </c>
-      <c r="B57" t="s">
-        <v>313</v>
-      </c>
       <c r="C57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" t="s">
         <v>185</v>
       </c>
-      <c r="D57" t="s">
-        <v>186</v>
-      </c>
       <c r="E57" t="s">
         <v>71</v>
       </c>
-      <c r="F57" s="29">
+      <c r="F57" s="26">
         <v>5920.32</v>
       </c>
       <c r="G57">
@@ -4444,21 +4438,21 @@
     </row>
     <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>313</v>
+      </c>
+      <c r="B58" t="s">
         <v>314</v>
       </c>
-      <c r="B58" t="s">
-        <v>315</v>
-      </c>
       <c r="C58" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" t="s">
         <v>187</v>
       </c>
-      <c r="D58" t="s">
-        <v>188</v>
-      </c>
       <c r="E58" t="s">
         <v>71</v>
       </c>
-      <c r="F58" s="29">
+      <c r="F58" s="26">
         <v>5759.33</v>
       </c>
       <c r="G58">
@@ -4467,21 +4461,21 @@
     </row>
     <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
+        <v>315</v>
+      </c>
+      <c r="B59" t="s">
         <v>316</v>
       </c>
-      <c r="B59" t="s">
-        <v>317</v>
-      </c>
       <c r="C59" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" t="s">
         <v>189</v>
       </c>
-      <c r="D59" t="s">
-        <v>190</v>
-      </c>
       <c r="E59" t="s">
         <v>71</v>
       </c>
-      <c r="F59" s="29">
+      <c r="F59" s="26">
         <v>5463.54</v>
       </c>
       <c r="G59">
@@ -4490,21 +4484,21 @@
     </row>
     <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" t="s">
         <v>318</v>
       </c>
-      <c r="B60" t="s">
-        <v>319</v>
-      </c>
       <c r="C60" t="s">
+        <v>190</v>
+      </c>
+      <c r="D60" t="s">
         <v>191</v>
       </c>
-      <c r="D60" t="s">
-        <v>192</v>
-      </c>
       <c r="E60" t="s">
         <v>71</v>
       </c>
-      <c r="F60" s="29">
+      <c r="F60" s="26">
         <v>4827.96</v>
       </c>
       <c r="G60">
@@ -4513,21 +4507,21 @@
     </row>
     <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>319</v>
+      </c>
+      <c r="B61" t="s">
         <v>320</v>
       </c>
-      <c r="B61" t="s">
-        <v>321</v>
-      </c>
       <c r="C61" t="s">
+        <v>192</v>
+      </c>
+      <c r="D61" t="s">
         <v>193</v>
       </c>
-      <c r="D61" t="s">
-        <v>194</v>
-      </c>
       <c r="E61" t="s">
         <v>71</v>
       </c>
-      <c r="F61" s="29">
+      <c r="F61" s="26">
         <v>4827.96</v>
       </c>
       <c r="G61">
@@ -4545,12 +4539,12 @@
         <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E62" t="s">
         <v>71</v>
       </c>
-      <c r="F62" s="29">
+      <c r="F62" s="26">
         <v>4572.88</v>
       </c>
       <c r="G62">
@@ -4559,21 +4553,21 @@
     </row>
     <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>321</v>
+      </c>
+      <c r="B63" t="s">
         <v>322</v>
       </c>
-      <c r="B63" t="s">
-        <v>323</v>
-      </c>
       <c r="C63" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" t="s">
         <v>196</v>
       </c>
-      <c r="D63" t="s">
-        <v>197</v>
-      </c>
       <c r="E63" t="s">
         <v>71</v>
       </c>
-      <c r="F63" s="29">
+      <c r="F63" s="26">
         <v>4405.93</v>
       </c>
       <c r="G63">
@@ -4582,21 +4576,21 @@
     </row>
     <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>323</v>
+      </c>
+      <c r="B64" t="s">
         <v>324</v>
       </c>
-      <c r="B64" t="s">
-        <v>325</v>
-      </c>
       <c r="C64" t="s">
+        <v>197</v>
+      </c>
+      <c r="D64" t="s">
         <v>198</v>
       </c>
-      <c r="D64" t="s">
-        <v>199</v>
-      </c>
       <c r="E64" t="s">
         <v>71</v>
       </c>
-      <c r="F64" s="29">
+      <c r="F64" s="26">
         <v>4236.4399999999996</v>
       </c>
       <c r="G64">
@@ -4605,21 +4599,21 @@
     </row>
     <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>325</v>
+      </c>
+      <c r="B65" t="s">
         <v>326</v>
       </c>
-      <c r="B65" t="s">
-        <v>327</v>
-      </c>
       <c r="C65" t="s">
+        <v>199</v>
+      </c>
+      <c r="D65" t="s">
         <v>200</v>
       </c>
-      <c r="D65" t="s">
-        <v>201</v>
-      </c>
       <c r="E65" t="s">
         <v>71</v>
       </c>
-      <c r="F65" s="29">
+      <c r="F65" s="26">
         <v>3982.2</v>
       </c>
       <c r="G65">
@@ -4628,21 +4622,21 @@
     </row>
     <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" t="s">
         <v>84</v>
       </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>85</v>
-      </c>
       <c r="D66" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E66" t="s">
         <v>71</v>
       </c>
-      <c r="F66" s="29">
+      <c r="F66" s="26">
         <v>3982.2</v>
       </c>
       <c r="G66">
@@ -4660,12 +4654,12 @@
         <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E67" t="s">
         <v>71</v>
       </c>
-      <c r="F67" s="29">
+      <c r="F67" s="26">
         <v>3388.13</v>
       </c>
       <c r="G67">
@@ -4683,12 +4677,12 @@
         <v>55</v>
       </c>
       <c r="D68" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E68" t="s">
         <v>71</v>
       </c>
-      <c r="F68" s="29">
+      <c r="F68" s="26">
         <v>3302.54</v>
       </c>
       <c r="G68">
@@ -4697,21 +4691,21 @@
     </row>
     <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>327</v>
+      </c>
+      <c r="B69" t="s">
         <v>328</v>
       </c>
-      <c r="B69" t="s">
-        <v>329</v>
-      </c>
       <c r="C69" t="s">
+        <v>204</v>
+      </c>
+      <c r="D69" t="s">
         <v>205</v>
       </c>
-      <c r="D69" t="s">
-        <v>206</v>
-      </c>
       <c r="E69" t="s">
         <v>71</v>
       </c>
-      <c r="F69" s="29">
+      <c r="F69" s="26">
         <v>3261.86</v>
       </c>
       <c r="G69">
@@ -4720,21 +4714,21 @@
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>329</v>
+      </c>
+      <c r="B70" t="s">
         <v>330</v>
       </c>
-      <c r="B70" t="s">
-        <v>331</v>
-      </c>
       <c r="C70" t="s">
+        <v>206</v>
+      </c>
+      <c r="D70" t="s">
         <v>207</v>
       </c>
-      <c r="D70" t="s">
-        <v>208</v>
-      </c>
       <c r="E70" t="s">
         <v>71</v>
       </c>
-      <c r="F70" s="29">
+      <c r="F70" s="26">
         <v>3218.64</v>
       </c>
       <c r="G70">
@@ -4743,21 +4737,21 @@
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>331</v>
+      </c>
+      <c r="B71" t="s">
         <v>332</v>
       </c>
-      <c r="B71" t="s">
-        <v>333</v>
-      </c>
       <c r="C71" t="s">
+        <v>208</v>
+      </c>
+      <c r="D71" t="s">
         <v>209</v>
       </c>
-      <c r="D71" t="s">
-        <v>210</v>
-      </c>
       <c r="E71" t="s">
         <v>71</v>
       </c>
-      <c r="F71" s="29">
+      <c r="F71" s="26">
         <v>3045.76</v>
       </c>
       <c r="G71">
@@ -4766,21 +4760,21 @@
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>333</v>
+      </c>
+      <c r="B72" t="s">
         <v>334</v>
       </c>
-      <c r="B72" t="s">
-        <v>335</v>
-      </c>
       <c r="C72" t="s">
+        <v>210</v>
+      </c>
+      <c r="D72" t="s">
         <v>211</v>
       </c>
-      <c r="D72" t="s">
-        <v>212</v>
-      </c>
       <c r="E72" t="s">
         <v>71</v>
       </c>
-      <c r="F72" s="29">
+      <c r="F72" s="26">
         <v>2761.01</v>
       </c>
       <c r="G72">
@@ -4789,21 +4783,21 @@
     </row>
     <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D73" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E73" t="s">
         <v>71</v>
       </c>
-      <c r="F73" s="29">
+      <c r="F73" s="26">
         <v>2710.16</v>
       </c>
       <c r="G73">
@@ -4812,21 +4806,21 @@
     </row>
     <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>336</v>
+      </c>
+      <c r="B74" t="s">
         <v>337</v>
       </c>
-      <c r="B74" t="s">
-        <v>338</v>
-      </c>
       <c r="C74" t="s">
+        <v>213</v>
+      </c>
+      <c r="D74" t="s">
         <v>214</v>
       </c>
-      <c r="D74" t="s">
-        <v>215</v>
-      </c>
       <c r="E74" t="s">
         <v>71</v>
       </c>
-      <c r="F74" s="29">
+      <c r="F74" s="26">
         <v>2668.64</v>
       </c>
       <c r="G74">
@@ -4835,21 +4829,21 @@
     </row>
     <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>338</v>
+      </c>
+      <c r="B75" t="s">
         <v>339</v>
       </c>
-      <c r="B75" t="s">
-        <v>340</v>
-      </c>
       <c r="C75" t="s">
+        <v>215</v>
+      </c>
+      <c r="D75" t="s">
         <v>216</v>
       </c>
-      <c r="D75" t="s">
-        <v>217</v>
-      </c>
       <c r="E75" t="s">
         <v>71</v>
       </c>
-      <c r="F75" s="29">
+      <c r="F75" s="26">
         <v>2031.36</v>
       </c>
       <c r="G75">
@@ -4867,12 +4861,12 @@
         <v>46</v>
       </c>
       <c r="D76" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E76" t="s">
         <v>71</v>
       </c>
-      <c r="F76" s="29">
+      <c r="F76" s="26">
         <v>1990.68</v>
       </c>
       <c r="G76">
@@ -4881,21 +4875,21 @@
     </row>
     <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B77" t="s">
         <v>45</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E77" t="s">
         <v>71</v>
       </c>
-      <c r="F77" s="29">
+      <c r="F77" s="26">
         <v>1990.68</v>
       </c>
       <c r="G77">
@@ -4913,12 +4907,12 @@
         <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E78" t="s">
         <v>71</v>
       </c>
-      <c r="F78" s="29">
+      <c r="F78" s="26">
         <v>1609.32</v>
       </c>
       <c r="G78">
@@ -4936,12 +4930,12 @@
         <v>73</v>
       </c>
       <c r="D79" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E79" t="s">
         <v>71</v>
       </c>
-      <c r="F79" s="29">
+      <c r="F79" s="26">
         <v>1439.84</v>
       </c>
       <c r="G79">
@@ -4950,21 +4944,21 @@
     </row>
     <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>341</v>
+      </c>
+      <c r="B80" t="s">
         <v>342</v>
       </c>
-      <c r="B80" t="s">
-        <v>343</v>
-      </c>
       <c r="C80" t="s">
+        <v>221</v>
+      </c>
+      <c r="D80" t="s">
         <v>222</v>
       </c>
-      <c r="D80" t="s">
-        <v>223</v>
-      </c>
       <c r="E80" t="s">
         <v>71</v>
       </c>
-      <c r="F80" s="29">
+      <c r="F80" s="26">
         <v>1438.98</v>
       </c>
       <c r="G80">
@@ -4973,21 +4967,21 @@
     </row>
     <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>343</v>
+      </c>
+      <c r="B81" t="s">
         <v>344</v>
       </c>
-      <c r="B81" t="s">
-        <v>345</v>
-      </c>
       <c r="C81" t="s">
+        <v>223</v>
+      </c>
+      <c r="D81" t="s">
         <v>224</v>
       </c>
-      <c r="D81" t="s">
-        <v>225</v>
-      </c>
       <c r="E81" t="s">
         <v>71</v>
       </c>
-      <c r="F81" s="29">
+      <c r="F81" s="26">
         <v>1141.52</v>
       </c>
       <c r="G81">
@@ -4996,21 +4990,21 @@
     </row>
     <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>345</v>
+      </c>
+      <c r="B82" t="s">
         <v>346</v>
       </c>
-      <c r="B82" t="s">
-        <v>347</v>
-      </c>
       <c r="C82" t="s">
+        <v>225</v>
+      </c>
+      <c r="D82" t="s">
         <v>226</v>
       </c>
-      <c r="D82" t="s">
-        <v>227</v>
-      </c>
       <c r="E82" t="s">
         <v>71</v>
       </c>
-      <c r="F82" s="29">
+      <c r="F82" s="26">
         <v>464.02</v>
       </c>
       <c r="G82">
@@ -5019,21 +5013,21 @@
     </row>
     <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>347</v>
+      </c>
+      <c r="B83" t="s">
         <v>348</v>
       </c>
-      <c r="B83" t="s">
-        <v>349</v>
-      </c>
       <c r="C83" t="s">
+        <v>227</v>
+      </c>
+      <c r="D83" t="s">
         <v>228</v>
       </c>
-      <c r="D83" t="s">
-        <v>229</v>
-      </c>
       <c r="E83" t="s">
         <v>71</v>
       </c>
-      <c r="F83" s="29">
+      <c r="F83" s="26">
         <v>0</v>
       </c>
       <c r="G83">
@@ -5042,21 +5036,21 @@
     </row>
     <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>349</v>
+      </c>
+      <c r="B84" t="s">
         <v>350</v>
       </c>
-      <c r="B84" t="s">
-        <v>351</v>
-      </c>
       <c r="C84" t="s">
+        <v>229</v>
+      </c>
+      <c r="D84" t="s">
         <v>230</v>
       </c>
-      <c r="D84" t="s">
-        <v>231</v>
-      </c>
       <c r="E84" t="s">
         <v>71</v>
       </c>
-      <c r="F84" s="29">
+      <c r="F84" s="26">
         <v>0</v>
       </c>
       <c r="G84">
@@ -5065,21 +5059,21 @@
     </row>
     <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>351</v>
+      </c>
+      <c r="B85" t="s">
         <v>352</v>
       </c>
-      <c r="B85" t="s">
-        <v>353</v>
-      </c>
       <c r="C85" t="s">
+        <v>231</v>
+      </c>
+      <c r="D85" t="s">
         <v>232</v>
       </c>
-      <c r="D85" t="s">
-        <v>233</v>
-      </c>
       <c r="E85" t="s">
         <v>71</v>
       </c>
-      <c r="F85" s="29">
+      <c r="F85" s="26">
         <v>0</v>
       </c>
       <c r="G85">
@@ -5088,21 +5082,21 @@
     </row>
     <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>353</v>
+      </c>
+      <c r="B86" t="s">
         <v>354</v>
       </c>
-      <c r="B86" t="s">
-        <v>355</v>
-      </c>
       <c r="C86" t="s">
+        <v>233</v>
+      </c>
+      <c r="D86" t="s">
         <v>234</v>
       </c>
-      <c r="D86" t="s">
-        <v>235</v>
-      </c>
       <c r="E86" t="s">
         <v>71</v>
       </c>
-      <c r="F86" s="29">
+      <c r="F86" s="26">
         <v>0</v>
       </c>
       <c r="G86">
@@ -5111,21 +5105,21 @@
     </row>
     <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>355</v>
+      </c>
+      <c r="B87" t="s">
         <v>356</v>
       </c>
-      <c r="B87" t="s">
-        <v>357</v>
-      </c>
       <c r="C87" t="s">
+        <v>235</v>
+      </c>
+      <c r="D87" t="s">
         <v>236</v>
       </c>
-      <c r="D87" t="s">
-        <v>237</v>
-      </c>
       <c r="E87" t="s">
         <v>71</v>
       </c>
-      <c r="F87" s="29">
+      <c r="F87" s="26">
         <v>0</v>
       </c>
       <c r="G87">
@@ -5134,21 +5128,21 @@
     </row>
     <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>357</v>
+      </c>
+      <c r="B88" t="s">
         <v>358</v>
       </c>
-      <c r="B88" t="s">
-        <v>359</v>
-      </c>
       <c r="C88" t="s">
+        <v>237</v>
+      </c>
+      <c r="D88" t="s">
         <v>238</v>
       </c>
-      <c r="D88" t="s">
-        <v>239</v>
-      </c>
       <c r="E88" t="s">
         <v>71</v>
       </c>
-      <c r="F88" s="29">
+      <c r="F88" s="26">
         <v>0</v>
       </c>
       <c r="G88">
@@ -5301,256 +5295,256 @@
       <c r="AA1" s="5"/>
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="20">
         <v>1</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="20">
         <v>2881</v>
       </c>
-      <c r="F2" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>79</v>
+      <c r="F2" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="23">
         <v>1</v>
       </c>
       <c r="E3" s="12">
         <v>2415.25</v>
       </c>
-      <c r="F3" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="B4" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="C4" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="19">
+      <c r="D4" s="17">
         <v>1</v>
       </c>
       <c r="E4" s="12">
         <v>2542.37</v>
       </c>
-      <c r="F4" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>80</v>
+      <c r="F4" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="17">
         <v>1</v>
       </c>
       <c r="E5" s="12">
         <v>1398.31</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>80</v>
+      <c r="F5" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="17">
         <v>1</v>
       </c>
       <c r="E6" s="12">
         <v>3114.41</v>
       </c>
-      <c r="F6" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>80</v>
+      <c r="F6" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="C7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="19">
+      <c r="D7" s="17">
         <v>1</v>
       </c>
       <c r="E7" s="12">
         <v>2987.29</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>80</v>
+      <c r="F7" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="C8" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="19">
+      <c r="D8" s="17">
         <v>1</v>
       </c>
       <c r="E8" s="12">
         <v>2415.25</v>
       </c>
-      <c r="F8" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>80</v>
+      <c r="F8" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="17">
         <v>1</v>
       </c>
       <c r="E9" s="12">
         <v>1271.19</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>80</v>
+      <c r="F9" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="17">
         <v>1</v>
       </c>
       <c r="E10" s="12">
         <v>762.71</v>
       </c>
-      <c r="F10" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>80</v>
+      <c r="F10" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="17">
         <v>1</v>
       </c>
       <c r="E11" s="12">
         <v>5719.71</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>92</v>
+      <c r="F11" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="19">
+      <c r="C12" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="17">
         <v>1</v>
       </c>
       <c r="E12" s="11">
         <v>14935</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>92</v>
+      <c r="F12" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
